--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-section-antecedents-familiaux.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-section-antecedents-familiaux.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="318">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,6 +536,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -725,6 +728,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -735,10 +741,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -751,6 +772,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -758,6 +788,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -765,6 +798,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -918,6 +954,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1294,7 +1336,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4951,7 +4993,9 @@
       <c r="K36" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="L36" s="2"/>
+      <c r="L36" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5022,10 +5066,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5059,7 +5103,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>74</v>
@@ -5081,7 +5125,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5099,7 +5143,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5119,10 +5163,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5156,7 +5200,7 @@
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>74</v>
@@ -5178,7 +5222,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5196,7 +5240,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5216,10 +5260,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5233,7 +5277,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5245,10 +5289,10 @@
         <v>95</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5299,7 +5343,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5319,10 +5363,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5336,7 +5380,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5345,13 +5389,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5402,7 +5446,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5422,10 +5466,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5523,10 +5567,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5555,7 +5599,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5567,7 +5611,7 @@
         <v>74</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>74</v>
@@ -5606,7 +5650,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5626,17 +5670,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>75</v>
@@ -5658,7 +5702,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5670,7 +5714,7 @@
         <v>74</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>74</v>
@@ -5709,7 +5753,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5729,17 +5773,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5761,7 +5805,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5773,7 +5817,7 @@
         <v>74</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>74</v>
@@ -5812,7 +5856,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5832,17 +5876,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5864,7 +5908,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5915,7 +5959,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5935,17 +5979,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>75</v>
@@ -5967,7 +6011,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5979,7 +6023,7 @@
         <v>74</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>74</v>
@@ -6018,7 +6062,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6038,10 +6082,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6064,11 +6108,11 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6119,7 +6163,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6139,10 +6183,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6169,7 +6213,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6220,7 +6264,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6240,17 +6284,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6268,11 +6312,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6323,7 +6367,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6343,17 +6387,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6371,11 +6415,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6426,7 +6470,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6446,17 +6490,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
@@ -6474,11 +6518,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6529,7 +6573,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6549,10 +6593,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6566,7 +6610,7 @@
         <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6575,16 +6619,18 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6632,7 +6678,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6652,10 +6698,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6669,7 +6715,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6678,15 +6724,17 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>74</v>
@@ -6735,7 +6783,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6755,10 +6803,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6781,12 +6829,16 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -6834,7 +6886,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6854,10 +6906,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6882,10 +6934,14 @@
       <c r="K55" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L55" s="2"/>
+      <c r="L55" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>74</v>
       </c>
@@ -6913,7 +6969,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6931,7 +6987,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6951,10 +7007,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6977,12 +7033,18 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="L56" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>74</v>
       </c>
@@ -7030,7 +7092,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7050,10 +7112,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7076,12 +7138,14 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>74</v>
       </c>
@@ -7129,7 +7193,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7149,10 +7213,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7175,12 +7239,14 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>74</v>
       </c>
@@ -7228,7 +7294,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7248,10 +7314,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7265,7 +7331,7 @@
         <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7274,10 +7340,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7329,7 +7395,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7349,10 +7415,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7450,10 +7516,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7551,10 +7617,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7652,10 +7718,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7753,10 +7819,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7856,10 +7922,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7959,10 +8025,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8062,10 +8128,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8165,10 +8231,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8266,10 +8332,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8299,7 +8365,7 @@
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
@@ -8325,7 +8391,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8343,7 +8409,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8363,10 +8429,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8400,7 +8466,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>74</v>
@@ -8442,7 +8508,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8462,10 +8528,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8488,7 +8554,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8541,7 +8607,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8561,10 +8627,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8587,7 +8653,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8640,7 +8706,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8660,10 +8726,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8686,7 +8752,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8739,7 +8805,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8759,10 +8825,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8785,7 +8851,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8838,7 +8904,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8858,10 +8924,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8884,7 +8950,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8937,7 +9003,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8957,10 +9023,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8983,7 +9049,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9036,7 +9102,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9056,10 +9122,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9082,7 +9148,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9135,7 +9201,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9155,10 +9221,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9181,7 +9247,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9234,7 +9300,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9254,10 +9320,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9280,7 +9346,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9333,7 +9399,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9353,10 +9419,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9379,12 +9445,16 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L80" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>74</v>
       </c>
@@ -9432,7 +9502,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9452,10 +9522,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9553,10 +9623,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9654,10 +9724,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9755,10 +9825,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9856,10 +9926,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9959,10 +10029,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10062,10 +10132,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10165,10 +10235,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10268,10 +10338,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10369,10 +10439,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10399,7 +10469,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10408,7 +10478,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>74</v>
@@ -10450,7 +10520,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10470,10 +10540,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10507,7 +10577,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>74</v>
@@ -10549,7 +10619,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10569,10 +10639,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10595,7 +10665,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10648,7 +10718,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
